--- a/Databases/Database3/Output/2015/db3_2015_geo_validated.xlsx
+++ b/Databases/Database3/Output/2015/db3_2015_geo_validated.xlsx
@@ -521,7 +521,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1021-1220</t>
+          <t>10:21 - 12:20</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>UL:S; UR:FW; LR:OB</t>
+          <t>UL:S; LL:-; UR:FW; LR:OB</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -593,7 +593,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1021-1220</t>
+          <t>10:21 - 12:20</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1021-1220</t>
+          <t>10:21 - 12:20</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>UL:FG; LL:BO; LR:WB</t>
+          <t>UL:FG; LL:BO; UR:-; LR:WB</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1021-1220</t>
+          <t>10:21 - 12:20</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -767,7 +767,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>UL:O; LL:O/Y; UR:S</t>
+          <t>UL:O; LL:O/Y; UR:S; LR:-</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1021-1220</t>
+          <t>10:21 - 12:20</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1021-1220</t>
+          <t>10:21 - 12:20</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1021-1220</t>
+          <t>10:21 - 12:20</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1021-1220</t>
+          <t>10:21 - 12:20</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1047,7 +1047,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>UL:O; LL:Lb; UR:S</t>
+          <t>UL:O; LL:Lb; UR:S; LR:-</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1021-1220</t>
+          <t>10:21 - 12:20</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1021-1220</t>
+          <t>10:21 - 12:20</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>9:17-10:57</t>
+          <t>09:17 - 10:57</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>8:12 - 10:12</t>
+          <t>08:12 - 10:12</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>8:12 - 10:12</t>
+          <t>08:12 - 10:12</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>8:12 - 10:12</t>
+          <t>08:12 - 10:12</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>9:00-11:45am</t>
+          <t>09:00 - 11:45</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1627,7 +1627,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>LR:A/B</t>
+          <t>UL:-; LL:-; UR:-; LR:A/B</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0900-1115</t>
+          <t>09:00 - 11:15</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0900-1115</t>
+          <t>09:00 - 11:15</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>07:30-14:30 EST</t>
+          <t>07:30 - 14:30</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>07:30-14:30 EST</t>
+          <t>07:30 - 14:30</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>LL:G; UR:FG; LR:GK</t>
+          <t>UL:-; LL:G; UR:FG; LR:GK</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1933,7 +1933,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>07:30-14:30 EST</t>
+          <t>07:30 - 14:30</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1238-1500</t>
+          <t>12:38 - 15:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1238-1500</t>
+          <t>12:38 - 15:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>UL:FG; LL:BB; LR:Y</t>
+          <t>UL:FG; LL:BB; UR:-; LR:Y</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1238-1500</t>
+          <t>12:38 - 15:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1238-1500</t>
+          <t>12:38 - 15:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1415-1647</t>
+          <t>14:15 - 16:47</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1415-1647</t>
+          <t>14:15 - 16:47</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>LL:YO; UR:FG; LR:WY</t>
+          <t>UL:-; LL:YO; UR:FG; LR:WY</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1415-1647</t>
+          <t>14:15 - 16:47</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>UL:FY; UR:S</t>
+          <t>UL:FY; LL:-; UR:S; LR:-</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1415-1647</t>
+          <t>14:15 - 16:47</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1415-1647</t>
+          <t>14:15 - 16:47</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0900-1400</t>
+          <t>09:00 - 14:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0900-1400</t>
+          <t>09:00 - 14:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0900-1400</t>
+          <t>09:00 - 14:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0900-1400</t>
+          <t>09:00 - 14:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1130-1230</t>
+          <t>11:30 - 12:30</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1130-1230</t>
+          <t>11:30 - 12:30</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>12:34-2;45</t>
+          <t>12:34 - 02:45</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>11:00-3:30</t>
+          <t>11:00 - 03:30</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>11:00-3:30</t>
+          <t>11:00 - 03:30</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>11:00-3:30</t>
+          <t>11:00 - 03:30</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1100-1745</t>
+          <t>11:00 - 17:45</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3295,7 +3295,7 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>UL:O; UR:S; LR:Lg/O/Lg</t>
+          <t>UL:O; LL:-; UR:S; LR:Lg/O/Lg</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1100-1745</t>
+          <t>11:00 - 17:45</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>UL:FG; LL:BK; LR:GY</t>
+          <t>UL:FG; LL:BK; UR:-; LR:GY</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1100-1745</t>
+          <t>11:00 - 17:45</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>UL:G; LL:KK; UR:FG</t>
+          <t>UL:G; LL:KK; UR:FG; LR:-</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1100-1745</t>
+          <t>11:00 - 17:45</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1100-1745</t>
+          <t>11:00 - 17:45</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3575,7 +3575,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>UL:FG; LL:YB; LR:WR</t>
+          <t>UL:FG; LL:YB; UR:-; LR:WR</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>8:55-13:22</t>
+          <t>08:55 - 13:22</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>8:55-13:22</t>
+          <t>08:55 - 13:22</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>8:55-13:22</t>
+          <t>08:55 - 13:22</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Orientation:Horizontal; UL:Yf; UR:S</t>
+          <t>Orientation:Horizontal; UL:Yf; LL:-; UR:S; LR:-</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>8:55-13:22</t>
+          <t>08:55 - 13:22</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>UL:Gf; LL:OO; LR:WB</t>
+          <t>UL:Gf; LL:OO; UR:-; LR:WB</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>8:55-13:22</t>
+          <t>08:55 - 13:22</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>UL:Of; LL:RR; LR:bS</t>
+          <t>UL:Of; LL:RR; UR:-; LR:bS</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>8:55-13:22</t>
+          <t>08:55 - 13:22</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>8:55-13:22</t>
+          <t>08:55 - 13:22</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>8:55-13:22</t>
+          <t>08:55 - 13:22</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>9:00-12:30</t>
+          <t>09:00 - 12:30</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>9:00-12:30</t>
+          <t>09:00 - 12:30</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>9:00-12:30</t>
+          <t>09:00 - 12:30</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>9:00-12:30</t>
+          <t>09:00 - 12:30</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>8:20-10:20 am</t>
+          <t>08:20 - 10:20</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4511,7 +4511,7 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>UL:R; LL:G/B; LR:Y/G/R</t>
+          <t>UL:R; LL:G/B; UR:-; LR:Y/G/R</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>8:20-10:20 am</t>
+          <t>08:20 - 10:20</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4609,7 +4609,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>9:40 am - 12:10 pm</t>
+          <t>09:40 - 12:10</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4673,7 +4673,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>7:30 - 9:00 am</t>
+          <t>07:30 - 09:00</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1245-1430</t>
+          <t>12:45 - 14:30</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1245-1430</t>
+          <t>12:45 - 14:30</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>1040 -1415</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4963,7 +4963,11 @@
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>UL:-; LL:-; UR:-; LR:-</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr">
         <is>
           <t>3 PIPL banded (see Data Sheet 3) | Band: photo available</t>
@@ -4995,7 +4999,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>1040 -1415</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5033,7 +5037,11 @@
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>UL:-; LL:-; UR:-; LR:-</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr">
         <is>
           <t>3 PIPL banded (see Data Sheet 3) | Band: photo available</t>
@@ -5065,7 +5073,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>1040 -1415</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -5103,7 +5111,11 @@
         </is>
       </c>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>UL:-; LL:-; UR:-; LR:-</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr">
         <is>
           <t>3 PIPL banded (see Data Sheet 3) | Band: photo available</t>
@@ -5135,7 +5147,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>1040 -1415</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -5201,7 +5213,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>1040 - 1415</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -5239,7 +5251,11 @@
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>UL:-; LL:-; UR:-; LR:-</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr">
         <is>
           <t>2 PIPL banded (see Data Sheet 3) | Band: photo available</t>
@@ -5271,7 +5287,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1040 - 1415</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -5309,7 +5325,11 @@
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>UL:-; LL:-; UR:-; LR:-</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr">
         <is>
           <t>2 PIPL banded (see Data Sheet 3) | Band: photo available</t>
@@ -5341,7 +5361,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>1040 - 1415</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -5407,7 +5427,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>1040 - 1415</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -5445,7 +5465,11 @@
         </is>
       </c>
       <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>UL:-; LL:-; UR:-; LR:-</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr">
         <is>
           <t>4 PIPL banded (see Data Sheet 3) | Band: photo available</t>
@@ -5477,7 +5501,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>1040 - 1415</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -5515,7 +5539,11 @@
         </is>
       </c>
       <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>UL:-; LL:-; UR:-; LR:-</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr">
         <is>
           <t>4 PIPL banded (see Data Sheet 3) | Band: photo available</t>
@@ -5547,7 +5575,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>1040 - 1415</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5585,7 +5613,11 @@
         </is>
       </c>
       <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>UL:-; LL:-; UR:-; LR:-</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr">
         <is>
           <t>4 PIPL banded (see Data Sheet 3) | Band: photo available</t>
@@ -5617,7 +5649,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>1040 - 1415</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5655,7 +5687,11 @@
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>UL:-; LL:-; UR:-; LR:-</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr">
         <is>
           <t>4 PIPL banded (see Data Sheet 3) | Band: photo available</t>
@@ -5687,7 +5723,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>1040 - 1415</t>
+          <t>10:40 - 14:15</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5753,7 +5789,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>8:45-10:45</t>
+          <t>08:45 - 10:45</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5825,7 +5861,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>8:45-10:45</t>
+          <t>08:45 - 10:45</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5889,7 +5925,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>9:45-12:30</t>
+          <t>09:45 - 12:30</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5965,7 +6001,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>9:45-12:30</t>
+          <t>09:45 - 12:30</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -6039,7 +6075,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>9:45-12:30</t>
+          <t>09:45 - 12:30</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -6111,7 +6147,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>9:45-12:30</t>
+          <t>09:45 - 12:30</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -6175,7 +6211,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -6235,7 +6271,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -6295,7 +6331,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -6337,7 +6373,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>UL:S; LL:Lb or Lg; LR:0</t>
+          <t>UL:S; LL:Lb or Lg; UR:-; LR:0</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6371,7 +6407,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -6431,7 +6467,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -6491,7 +6527,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -6555,7 +6591,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -6619,7 +6655,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -6679,7 +6715,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -6721,7 +6757,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>UL:F(G); LL:B/B; LR:Y/W</t>
+          <t>UL:F(G); LL:B/B; UR:-; LR:Y/W</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -6755,7 +6791,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6797,7 +6833,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>UL:F(G); LL:K; UR:G</t>
+          <t>UL:F(G); LL:K; UR:G; LR:-</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -6831,7 +6867,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6895,7 +6931,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6937,7 +6973,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Orientation:horizontal; UL:S; UR:F(A)</t>
+          <t>Orientation:horizontal; UL:S; LL:-; UR:F(A); LR:-</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
@@ -6967,7 +7003,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>9:30 am - 12:30 pm</t>
+          <t>09:30 - 12:30</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -7027,7 +7063,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>09:12-10:35</t>
+          <t>09:12 - 10:35</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -7091,7 +7127,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>8:45-11:30</t>
+          <t>08:45 - 11:30</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -7167,7 +7203,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>8:45-11:30</t>
+          <t>08:45 - 11:30</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -7209,7 +7245,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>UL:F(W); UR:S</t>
+          <t>UL:F(W); LL:-; UR:S; LR:-</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7243,7 +7279,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>8:45-11:30</t>
+          <t>08:45 - 11:30</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -7285,7 +7321,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>UL:F(G); LL:W/O; UR:Y</t>
+          <t>UL:F(G); LL:W/O; UR:Y; LR:-</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7319,7 +7355,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>8:45-11:30</t>
+          <t>08:45 - 11:30</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -7361,7 +7397,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>LL:W/W; UR:F(G); LR:O/Y</t>
+          <t>UL:-; LL:W/W; UR:F(G); LR:O/Y</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7395,7 +7431,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>8:45-11:30</t>
+          <t>08:45 - 11:30</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -7471,7 +7507,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>8:45-11:30</t>
+          <t>08:45 - 11:30</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -7535,7 +7571,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>8:45-11:30</t>
+          <t>08:45 - 11:30</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -7599,7 +7635,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>10:30 AM-12:30 PM</t>
+          <t>10:30 - 12:30</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -7659,7 +7695,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>09:15 to 12:30</t>
+          <t>09:15 - 12:30</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -7731,7 +7767,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>09:15 to 12:30</t>
+          <t>09:15 - 12:30</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -7803,7 +7839,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>09:15 to 12:30</t>
+          <t>09:15 - 12:30</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -7867,7 +7903,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>09:15 to 12:30</t>
+          <t>09:15 - 12:30</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -7931,7 +7967,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>09:15 to 12:30</t>
+          <t>09:15 - 12:30</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -8037,7 +8073,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Orientation:Horizontal; UL:FY; UR:S</t>
+          <t>Orientation:Horizontal; UL:FY; LL:-; UR:S; LR:-</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8185,7 +8221,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>UL:FG; LL:BG; LR:WB</t>
+          <t>UL:FG; LL:BG; UR:-; LR:WB</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8261,7 +8297,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Orientation:Horizontal; UL:FY; LL:GB; LR:GP</t>
+          <t>Orientation:Horizontal; UL:FY; LL:GB; UR:-; LR:GP</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8789,7 +8825,7 @@
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
-          <t>UL:S; LL:BO</t>
+          <t>UL:S; LL:BO; UR:-; LR:-</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9023,7 +9059,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>07:45 / 17:30</t>
+          <t>07:45 - 17:30</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -9091,7 +9127,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>11:44-1:21</t>
+          <t>11:44 - 01:21</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -9151,7 +9187,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>11:44-1:21</t>
+          <t>11:44 - 01:21</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
